--- a/Field-trails/slurry acidification.xlsx
+++ b/Field-trails/slurry acidification.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Field-trails\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ED0919D-6C8A-47D8-8AC8-07DE0EF5ADFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{004299A8-DAF8-401C-845D-4F9E73E2FAF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -159,7 +159,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="170" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -210,16 +210,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -606,7 +603,7 @@
         <v>5.8</v>
       </c>
       <c r="I3" s="3">
-        <f t="shared" ref="I3:I7" si="0">(G3*10^-3) / (D3*10^-3)</f>
+        <f>(G3*10^-3) / (D3*10^-3)</f>
         <v>2.847666666666667</v>
       </c>
     </row>
@@ -633,7 +630,7 @@
         <v>5.88</v>
       </c>
       <c r="I4" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I4:I7" si="0">(G4*10^-3) / (D4*10^-3)</f>
         <v>3.2275379229871648</v>
       </c>
     </row>
@@ -723,25 +720,31 @@
         <v>10</v>
       </c>
     </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D11">
+        <f>0.1</f>
+        <v>0.1</v>
+      </c>
+    </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C14" s="5"/>
